--- a/AAII_Financials/Quarterly/IHRT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IHRT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
   <si>
     <t>IHRT</t>
   </si>
@@ -656,476 +656,489 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="37" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="38" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>977200</v>
+      </c>
+      <c r="E8" s="3">
         <v>884200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1127200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>997000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>933700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>807100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1118300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1008100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>929100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>799000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1066800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>953000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>920000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>811200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1125900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>988900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>954000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>843500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1062000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>928100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>861600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>706700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>935500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>744400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>487600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>780600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1026100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>948300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>913300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>795800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1026300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>920500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>891800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>772800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1711300</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>400600</v>
+      </c>
+      <c r="E9" s="3">
         <v>375100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>466800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>399100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>391200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>356300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>455800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>409700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>382000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>341400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>414600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>380000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>355100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>344600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>412700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>371700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>365400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>330500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>385600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>325800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>320500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>292800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>334900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>276700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>249900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>301600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>332100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>291000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>276900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>282900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>288900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>268600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>263800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>241100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>661200</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>576700</v>
+      </c>
+      <c r="E10" s="3">
         <v>509100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>660500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>597900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>542500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>450800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>662500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>598400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>547000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>457700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>652200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>573000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>565000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>466600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>713200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>617200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>588600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>513000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>676400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>602300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>541100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>413900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>600600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>467700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>237700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>479000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>694000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>657300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>636400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>512900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>737400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>651900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>628000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>531700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1050100</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1163,8 +1176,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1270,8 +1284,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1377,222 +1394,231 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E14" s="3">
         <v>500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>10300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>221800</v>
       </c>
-      <c r="G14" s="3">
-        <v>3700</v>
-      </c>
       <c r="H14" s="3">
+        <v>3500</v>
+      </c>
+      <c r="I14" s="3">
         <v>21400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>113800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>920600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-90500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-12800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>943700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>5500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-15000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>302900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-8000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>8300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>11600</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>37700</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>5500</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>5400</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1727900</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>-9497900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>133000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>42700</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>85600</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>68700</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>192000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>78300</v>
+      </c>
+      <c r="E15" s="3">
         <v>81400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>87700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>90100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>90400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>91900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>98700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>101300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>104400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>105200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>105500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>106500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>108100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>108500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>111500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>109300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>110800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>114100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>126000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>108100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>127900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>107400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>103400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>99400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>103300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>96800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>95000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>95300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>73900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>38300</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>36400</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>43300</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>64900</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>67400</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>157600</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1627,222 +1653,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>941700</v>
+      </c>
+      <c r="E17" s="3">
         <v>882700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1041500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>904800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>895700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>829700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1013200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>931000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>918500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>832200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>987000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>880300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>856600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>856400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>937900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1193200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>862900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>831100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>939000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>847900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>833500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>783000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>822700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>705000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>646700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2511400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>860900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>807500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>-8766200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>812800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>809200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>786100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>779300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>902700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1393300</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>35500</v>
+      </c>
+      <c r="E18" s="3">
         <v>1500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>85700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>92200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>37900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-22600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>105100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>77100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>10600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-33200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>79800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>72700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>63400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-45200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>188000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-204300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>91100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>12400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>123000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>80200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>28100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-76300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>112800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>39400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-159100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-1730800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>165200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>140800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>9679500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-17000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>217100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>134400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>112500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-129900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>318000</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1880,267 +1913,274 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>500</v>
+      </c>
+      <c r="E20" s="3">
         <v>400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>6900</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I20" s="3">
         <v>1100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>4300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-97600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-92000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-74100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-81300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-79800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-103600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-35600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-85800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-84000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-86700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-81900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-108400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-115700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-111700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-78400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>104500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>86800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>97000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>522400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>76800</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-7100</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>113400</v>
+      </c>
+      <c r="E21" s="3">
         <v>82500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>166500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>182300</v>
       </c>
-      <c r="G21" s="3">
-        <v>129200</v>
-      </c>
       <c r="H21" s="3">
+        <v>129000</v>
+      </c>
+      <c r="I21" s="3">
         <v>68200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>202500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>177100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>114600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>71400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>185700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>174900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>171100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>63300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>201900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-187100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>127800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>45100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>169100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>84600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>120400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-54800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>132200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>52000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-137700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-1742500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>144400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>124400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>9600000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>200900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>659300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>274700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>615800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>98300</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>468600</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>96100</v>
+      </c>
+      <c r="E22" s="3">
         <v>95900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>99500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>101800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>100900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>100400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>92600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>95700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>95600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>95500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>96100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>99500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>98700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>95500</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -2165,8 +2205,8 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>8</v>
+      <c r="Z22" s="3">
+        <v>0</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>8</v>
@@ -2183,240 +2223,249 @@
       <c r="AE22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AF22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG22" s="3">
         <v>114800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>97700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>99300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>526000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>418400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>475400</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-62600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-95300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-31100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-231400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-65700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-145500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-102700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-20500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1005900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-38800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-18900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-18200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-979300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-146300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>90400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-296400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>17000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-68900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>43100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-23500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-7500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-162100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>28800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-47300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-241100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1839200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>49500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>29100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>9601100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-27200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>206300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>132100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>109000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-471500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-164500</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>10200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-165600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>18300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>135400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-134600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>20800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-24000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-20700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-32800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-9300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-96400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>76100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>9700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>13400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-20200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-68800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-27100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>24400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>79900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>25900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-15200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-43700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-150500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-12700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>16800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>116300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-61200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>23700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>10900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>142000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-162700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2522,222 +2571,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-82500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-95600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-41300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-65800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-84000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-280900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>31900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-41300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-982000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-18100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>14000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-883000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-222400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>80700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-309800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>15200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-48700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>112000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-32000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-242100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-32100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-197300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1688700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>62100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>12400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>9484800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>34000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>182600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>121300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-33100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-308800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-167000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-82400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-95200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-41900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-66300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-83500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-281200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>31500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-41300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-981700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-18500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>13100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-884500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-222300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>79900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-310400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>14400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-48600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>111600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-32300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-241700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-32100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-197300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1688700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>62100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>12400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>9484800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>55200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>172600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>119600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-20600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-292700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-97700</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2843,8 +2901,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2905,14 +2966,14 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z29" s="3">
         <v>0</v>
@@ -2924,34 +2985,37 @@
         <v>0</v>
       </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-800</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
       <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>1852500</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-317900</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>32300</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-51200</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-36800</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-108200</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>510100</v>
       </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3057,8 +3121,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3164,222 +3231,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-6900</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>700</v>
+      </c>
+      <c r="I32" s="3">
         <v>-1100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-4300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>97600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>92000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>74100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>81300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>79800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>103600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>35600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>85800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>84000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>86700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>81900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>108400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>115700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>111700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>78400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-104500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-86800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-97000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-522400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-76800</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-82400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-95200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-41900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-66300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-83500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-281200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>31500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-41300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-981700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-18500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>13100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-884500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-222300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>79900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-310400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>14400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-48600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>111600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-32300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-241700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-32100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-197300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1688700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>61400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>12400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>11337300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-262700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>204900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>68400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-57500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-400900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>412400</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3485,227 +3561,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-82400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-95200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-41900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-66300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-83500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-281200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>31500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-41300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-981700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-18500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>13100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-884500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-222300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>79900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-310400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>14400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-48600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>111600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-32300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-241700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-32100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-197300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1688700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>61400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>12400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>11337300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-262700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>204900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>68400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-57500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-400900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>412400</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3743,8 +3828,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3782,115 +3868,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>174400</v>
+      </c>
+      <c r="E41" s="3">
         <v>135100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>270900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>192200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>235900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>167700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>259600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>431800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>364700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>361400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>346400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>213500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>165300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>187900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>336200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>295400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>294800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>279700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>352100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>369100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>583300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>529100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>720700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>713700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>517700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>646800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>400300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>277100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>127200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>448100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>224000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>311200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>261800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>297400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>267100</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3996,115 +4086,121 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>820300</v>
+      </c>
+      <c r="E43" s="3">
         <v>853600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>959400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>845800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>879100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>817500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>993300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>894500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>898500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>878400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1041200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>983900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1004800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>935200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1037800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>981100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>967100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>906900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1030400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>858000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>788900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>704100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>801400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>665900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>570100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>749900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>902900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>843200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>843100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1387100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>868900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1466900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1419000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1367000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1508400</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4147,8 +4243,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4210,233 +4306,242 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E45" s="3">
         <v>54500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>38600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>100100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>83200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>34300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>11600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>33800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>18800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>38100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>26200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>38900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>35700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>98700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>132000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>110200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>129300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>90400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>129000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>138800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>132900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>96900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>116900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>121700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>128300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>113100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>150900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>143500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>254800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1200200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>300700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>342600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>417800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>291900</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1290400</v>
+      </c>
+      <c r="E46" s="3">
         <v>1285500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1459300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1354400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1348200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1159600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1361800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1508000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1422300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1413100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1506900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1349000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1336400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1271300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1472800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1408600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1372100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1315900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1472900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1356000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1511000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1366100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1619000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1496500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1209500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1525000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1416300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1271200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1113700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2090100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2235000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2078800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2023400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>2082200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>2067300</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3">
         <v>182100</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>8</v>
@@ -4444,11 +4549,11 @@
       <c r="H47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3">
         <v>168500</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>8</v>
@@ -4456,11 +4561,11 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="3">
         <v>134200</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>8</v>
@@ -4468,8 +4573,8 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -4531,222 +4636,231 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>992600</v>
+      </c>
+      <c r="E48" s="3">
         <v>1002500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1024000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1070800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1092600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1121400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1158000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1171100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1196100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1222700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1263900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1294800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1350400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1445200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1483100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1484100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1524200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1476200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1523500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1517500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1561000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1606700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1637600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1648700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1660100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1700600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1728600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1720300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1735000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>4100500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2293300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1719100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1755300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1838800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>4950300</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2320200</v>
+      </c>
+      <c r="E49" s="3">
         <v>2370200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2420700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2473400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2735600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2789100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2842700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2904100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2965600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3947100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4008700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4068300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4130300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5147600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5209400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5266800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5631800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5695000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5758200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5821200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5878100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5966100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5840800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5871500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5925300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>5988400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>7779900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>7841700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>7911300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>7855900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>7455500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>7865400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>7929400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>7986200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>8580200</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4852,8 +4966,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4959,115 +5076,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>250900</v>
+      </c>
+      <c r="E52" s="3">
         <v>229700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>39900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>189900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>203000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>198000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>40700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>195800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>185200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>175500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>38900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>165400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>166800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>171000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>170600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>170200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>172900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>139900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>126700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>115900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>114000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>112100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>105600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>105400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>110900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>98100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>96200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>101700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>237800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>239500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>3501200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>296000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>278200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>285800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>278300</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5173,115 +5296,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4854100</v>
+      </c>
+      <c r="E54" s="3">
         <v>4887900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5126000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5088600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5379300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5268100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5571700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5779000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5769200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6758300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6952600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6877500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6983800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8035200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8335900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8329700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>8701100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>8627000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>8881300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>8810600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>9064100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>9051000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>9203000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>9122100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>8905900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>9312100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>11021100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>10934900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>10997800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>14286000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>12269500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>11959300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>11986200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>12193000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>12260400</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5319,8 +5448,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5358,159 +5488,163 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>296000</v>
+      </c>
+      <c r="E57" s="3">
         <v>279900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>271400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>218500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>217100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>210000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>253300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>235800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>222100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>215400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>236200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>179700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>199900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>177300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>240500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>204900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>199000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>156900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>206000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>190100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>183200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>157000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>149300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>125900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>114400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>118400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>87400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>61400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>47900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>146900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>49400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>149200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>150000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>135900</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>163400</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>153200</v>
+      </c>
+      <c r="E58" s="3">
         <v>136800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>134400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>140900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>140500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>91300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>92000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>71400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>73200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>74100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>74200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>75900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>76200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>75600</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>700</v>
       </c>
       <c r="R58" s="3">
         <v>700</v>
@@ -5528,480 +5662,495 @@
         <v>700</v>
       </c>
       <c r="W58" s="3">
+        <v>700</v>
+      </c>
+      <c r="X58" s="3">
         <v>278300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>28600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>34800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>34400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>30100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>30000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>8900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>53700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>53400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>46700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>46100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>300</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>125400</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>800</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>14972400</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>177700</v>
+      </c>
+      <c r="E59" s="3">
         <v>191800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>190200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>154100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>178900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>165600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>154300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>162900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>160300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>163300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>158500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>172000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>160100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>144700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>590700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>534500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>558500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>530300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>642700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>591400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>557500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>547800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>533700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>500100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>448600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>497500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>571100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>521500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>624300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1246000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1152100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>994600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>968000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>845500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1218800</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>913300</v>
+      </c>
+      <c r="E60" s="3">
         <v>864300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>967400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>852300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>899100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>729800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>870300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>780300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>739000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>702100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>848400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>742700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>730800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>656700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>831800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>740000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>758200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>687800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>849400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>782300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1019100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>733500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>717800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>660400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>593100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>645800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>667400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>636600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>725600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1439600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1247600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1144200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1243400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>982300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>16354600</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5611300</v>
+      </c>
+      <c r="E61" s="3">
         <v>5629100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5653900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5729400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5757400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5737600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5765600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5942500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5955500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5965900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5977600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6000400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6078700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6227400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5413500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5553000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5626700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5739400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5738200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5796700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5781000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>6036400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6042200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6047400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>5867100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5983700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5816500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5815300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5817100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5293400</v>
       </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
       <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
         <v>5274500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5272100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>5636700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>5676800</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>234800</v>
+      </c>
+      <c r="E62" s="3">
         <v>222600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>230500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>196100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>186700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>189500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>185300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>172500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>153000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>150800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>148200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>140000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>127500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>96800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1406100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1443800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1422800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1327700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1377900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1433700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1475100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1467200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1392200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1374600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1380100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1423200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1591800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1636200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1635100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>19119100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>22582200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>17333800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>17333000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>17326700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1573400</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6107,8 +6256,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6214,8 +6366,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6321,115 +6476,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6862400</v>
+      </c>
+      <c r="E66" s="3">
         <v>6809900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6953000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6877300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7105600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6914200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6943500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7188400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7143800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7156900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7337400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7284300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7387300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7563300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7661000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7745900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7816400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7763100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7974000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>8020900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>8283200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>8244900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>8160500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>8091600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>7849300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>8061900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>8084800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>8096400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>8186100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>25863500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>23860700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>23769900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>23866400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>23976800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>23646000</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6467,8 +6628,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6574,8 +6736,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6681,8 +6846,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6788,8 +6956,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6895,115 +7066,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-4990600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-4908200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-4812900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-4771100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-4704800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-4621300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-4340100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-4371600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-4330300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-3348700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-3330100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-3343300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-3334200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-2449700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-2227500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-2307400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1997000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-2011400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-1962800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-2074400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-2077600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-2045300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-1803600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-1807100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-1775000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-1577700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>112500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>51200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>38800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-13330800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-13345300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-13560300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-13630300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-13543500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-13142000</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7109,8 +7286,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7216,8 +7396,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7323,115 +7506,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-2010700</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1925400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1831600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1793100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1730500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1651400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1377100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-1414700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-1380300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-405000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-394200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-415700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-413800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>462700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>674900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>583800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>884800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>864000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>907400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>789700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>780900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>806100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1042500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1030500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1056500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1250200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2936300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2838500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2811700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-11577600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-11591200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-11810600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>-11880200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>-11783800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>-11385500</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7537,227 +7726,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-82400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-95200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-41900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-66300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-83500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-281200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>31500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-41300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-981700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-18500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>13100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-884500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-222300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>79900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-310400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>14400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-48600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>111600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-32300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-241700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-32100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-197300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1688700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>61400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>12400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>11337300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-262700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>204900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>68400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-57500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-400900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>412400</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7795,115 +7993,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>36700</v>
+      </c>
+      <c r="E83" s="3">
         <v>38200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>37700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>40100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>43200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>43300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>44100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>44800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>46300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>46700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>47800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>45900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>47400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>51000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>111500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>109300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>110800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>114100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>126000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>108100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>127900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>107400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>103400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>99400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>103300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>96800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>95000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>95300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>113400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>111100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>120700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>147600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>151400</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>157600</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8009,8 +8211,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8116,8 +8321,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8223,8 +8431,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8330,8 +8541,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8437,115 +8651,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>64900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-92500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>156300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-9500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-60900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>102800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>26700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-59300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>154100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>96200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>56800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-94000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>213400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>103100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>155800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-52200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>134000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>95700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>29100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>71700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>79800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>33300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>11400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>91500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>205400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>180300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-46000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>89000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>303300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>219000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>268900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>175500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>66500</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8583,115 +8803,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-21900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-18700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-23300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-20000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-19700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-25400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-29400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-21200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-21600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-12200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-28500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-22800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-39200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-48400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-40400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-49700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-22600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-82000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-50300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-32100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-26700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-19000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-17900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-21700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-29700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-28900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-51100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-248900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-20100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>11400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-38700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-107000</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8797,8 +9021,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8904,115 +9131,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-21100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-23500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-8400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-17200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-20600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-20100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-23000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-32400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-22100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>78000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-11300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>19300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-20800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-38400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-46400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-33200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-30000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-19700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-86900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-41600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>31100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-249300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-76600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-20500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-18900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-31800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-29500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-26000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-226500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-52400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-210600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-56600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-41100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-37200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-94300</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9050,8 +9283,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9094,8 +9328,8 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -9137,28 +9371,31 @@
         <v>0</v>
       </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-500</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-100</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-8300</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>3800</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-1700</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-3200</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9264,8 +9501,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9371,8 +9611,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9478,325 +9721,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-19600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-69200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-16800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>81700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-11000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-149900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-10200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-67100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-58900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-15900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-126500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-68900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-110300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-64000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-268200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-6100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-13800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-7500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>183100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-121800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>187300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-52900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-4400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-58200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>2000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-132300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-268400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-92400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>300</v>
+      </c>
+      <c r="E101" s="3">
         <v>200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
         <v>0</v>
       </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>300</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-400</v>
       </c>
       <c r="O101" s="3">
         <v>-400</v>
       </c>
       <c r="P101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>300</v>
-      </c>
-      <c r="R101" s="3">
-        <v>-400</v>
       </c>
       <c r="S101" s="3">
         <v>-400</v>
       </c>
       <c r="T101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="U101" s="3">
         <v>-100</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>-100</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>400</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>200</v>
       </c>
       <c r="AA101" s="3">
         <v>200</v>
       </c>
       <c r="AB101" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC101" s="3">
         <v>-500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-1800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-3900</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-8100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>3400</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>39400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-135900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>78700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-43700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>68200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-91900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-172200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>67000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>15000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>132900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>48200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-23000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-148300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>40800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>15100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-72400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-17000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-214200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>54100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-191500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>196100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-129100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>246500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>123300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>149600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-330800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>39300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>92200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>26200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-48600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>49200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-10900</v>
       </c>
     </row>
